--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A04108B-528F-5340-BCDE-1C8A174E4A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6D5E9E-9369-4C46-A550-8E70F8F94229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Core_Schema_SIMPLIFIED" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>KS_evidence_present</t>
   </si>
   <si>
-    <t>Whether the contributor invokes an identifiable evidence item in support of the claim.</t>
-  </si>
-  <si>
     <t>Raw text: “Oxford English Dictionary ‘non-combatant’ … A person who is not a combatant, as a civilian during a war…”
 Explanation: The contributor invokes a specifically identifiable external source as evidence.</t>
   </si>
@@ -727,6 +724,9 @@
   </si>
   <si>
     <t>Whether the contributor asks others to assess, revise, or accept, their work.</t>
+  </si>
+  <si>
+    <t>Whether the contributor invokes (or references) an identifiable evidence item.</t>
   </si>
 </sst>
 </file>
@@ -1023,10 +1023,10 @@
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -1046,13 +1046,13 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>17</v>
@@ -1063,22 +1063,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="140.75" customHeight="1">
@@ -1086,22 +1086,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="F6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="258" customHeight="1">
@@ -1109,22 +1109,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="117.25" customHeight="1">
@@ -1132,42 +1132,42 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="117.25" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
@@ -1175,22 +1175,22 @@
     </row>
     <row r="10" spans="1:7" ht="117.25" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>17</v>
@@ -1198,22 +1198,22 @@
     </row>
     <row r="11" spans="1:7" ht="117.25" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -1221,91 +1221,91 @@
     </row>
     <row r="12" spans="1:7" ht="117.25" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="F12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="117.25" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="164.25" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="117.25" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -1313,91 +1313,91 @@
     </row>
     <row r="16" spans="1:7" ht="117.25" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="117.25" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="117.25" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="117.25" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -1455,10 +1455,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -1478,10 +1478,10 @@
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -1501,13 +1501,13 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>17</v>
@@ -1518,22 +1518,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="123.25" customHeight="1">
@@ -1541,22 +1541,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="193.5" customHeight="1">
@@ -1564,22 +1564,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="105.5" customHeight="1">
@@ -1587,42 +1587,42 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="88" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
@@ -1630,22 +1630,22 @@
     </row>
     <row r="10" spans="1:7" ht="88" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>17</v>
@@ -1653,22 +1653,22 @@
     </row>
     <row r="11" spans="1:7" ht="88" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>13</v>
@@ -1676,91 +1676,91 @@
     </row>
     <row r="12" spans="1:7" ht="88" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="88" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="123.25" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="88" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -1768,91 +1768,91 @@
     </row>
     <row r="16" spans="1:7" ht="88" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="F16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="88" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="105.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="88" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -1877,16 +1877,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -1897,142 +1897,142 @@
     </row>
     <row r="2" spans="1:6" ht="70.25" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="47" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="70.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="70.25" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="70.25" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="70.25" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="70.25" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2054,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -2071,138 +2071,138 @@
     </row>
     <row r="2" spans="1:5" ht="70.25" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="70.25" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="47" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="70.25" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="93.75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="47" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="70.25" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="117.25" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6D5E9E-9369-4C46-A550-8E70F8F94229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E1683C-4C85-1E47-AE31-30093D8C2D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,9 +697,6 @@
     <t>Only code if KI_present=1; otherwise null. Code 1 when the utterance explicitly asks for feedback, objections, agreement, review, or further revision of a possible resolution (e.g., a proposed edit). A generic “comments?” with no proposed or enacted edit, and a request for facts unrelated to a proposed/enacted edit are 0.</t>
   </si>
   <si>
-    <t>Whether the contributor explicitly accepts, rejects, or gives a mixed or conditional evaluation of an earlier proposed edit.</t>
-  </si>
-  <si>
     <t>Whether the edit or its evaluation visibly reuses knowledge staked earlier in the dispute.</t>
   </si>
   <si>
@@ -723,10 +720,13 @@
     <t>binary {0,1}; null unless KI_present=1 and an earlier KI attempt exists</t>
   </si>
   <si>
-    <t>Whether the contributor asks others to assess, revise, or accept, their work.</t>
-  </si>
-  <si>
     <t>Whether the contributor invokes (or references) an identifiable evidence item.</t>
+  </si>
+  <si>
+    <t>Whether the contributor asks others to assess, revise, or accept, proposed/enacted work.</t>
+  </si>
+  <si>
+    <t>Whether the contributor explicitly accepts, rejects, or gives a mixed or conditional evaluation of an earlier proposed/enacted edit.</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1046,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>167</v>
@@ -1247,13 +1247,13 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>200</v>
@@ -1276,13 +1276,13 @@
         <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>56</v>
@@ -1299,7 +1299,7 @@
         <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>173</v>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842A9852-E430-D644-B59C-C1222B2F1D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3391707-89D7-734C-B235-3E5DC5D519F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>binary {0,1}</t>
   </si>
   <si>
-    <t>Code 1 when the utterance asserts, challenges, or qualifies substantive knowledge relevant to the article or its evaluation. A question counts only when it asserts, presupposes, or challenges such knowledge. Code 0 for headings, greetings, pure coordination, or a pure insult with no substantive position. Code substantive opening utterances normally. KS and KI may both be 1.</t>
-  </si>
-  <si>
     <t>Raw text: “Anything else violates WP:NPOV and becomes WP:OR. This is Wikipedia policy and is non-negotiable.”
 Explanation: The contributor makes a substantive article-related position public.</t>
   </si>
@@ -231,9 +228,6 @@
     <t>binary {0,1}; null if KI_present=0 OR likert-5 {1,2,3,4,5}</t>
   </si>
   <si>
-    <t>Whether the utterance makes dispute-relevant knowledge public by asserting or challenging a substantive claim, observation, interpretation, or constraint relevant to the article or dispute.</t>
-  </si>
-  <si>
     <t>KS_restaking</t>
   </si>
   <si>
@@ -252,7 +246,13 @@
     <t xml:space="preserve">Whether the utterance coordinates an article edit by proposing one, announcing or reporting one, or refining one. </t>
   </si>
   <si>
-    <t>Code 1 when the utterance proposes a future edit, announces or reports an enacted edit, or refines an edit to article content, wording, sourcing, scope, structure, placement, or media. The exact changed text or diff need not be visible when the utterance clearly refers to an article edit (for example, “I changed it”). Code 0 for a pure claim, objection, acceptance, rejection, or evaluation that does not also coordinate an edit; most such feedback is KS. Also code 0 for generic process or governance steps and for Talk-page/WikiProject assessment metadata such as article grade. Also code 0 for discussion of reversion. KS and KI may co-occur.</t>
+    <t>Code 1 when the utterance proposes a future edit, announces or reports an enacted edit, or refines an edit to article content, wording, sourcing, scope, structure, placement, or media. The exact changed text or diff need not be visible when the utterance clearly refers to an article edit (for example, “I changed it”). Code 0 for a pure claim, objection, acceptance, rejection, or evaluation that does not also coordinate an edit; most such feedback is KS. Also code 0 for generic process or governance steps and for Talk-page/WikiProject assessment metadata such as article grade. Also code 0 for calls and offers to revert work. KS and KI may co-occur.</t>
+  </si>
+  <si>
+    <t>Whether the utterance makes dispute-relevant knowledge public by asserting or challenging a claim, observation, interpretation, or constraint relevant to the article or dispute.</t>
+  </si>
+  <si>
+    <t>Code 1 when the utterance asserts, challenges, or qualifies knowledge relevant to the article or its evaluation. A question counts only when it asserts, presupposes, or challenges knowledge. Code 0 for headings, greetings, pure coordination, or a pure insult with no substantive position. KS and KI may both be 1.</t>
   </si>
 </sst>
 </file>
@@ -592,16 +592,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="120.75" customHeight="1">
@@ -609,22 +609,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="148.75" customHeight="1">
@@ -632,22 +632,22 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="118.75" customHeight="1">
@@ -655,22 +655,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="104" customHeight="1">
@@ -678,179 +678,179 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" ht="134.5" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="110.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="133" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="101.75" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="96.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="114.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="242.5" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3391707-89D7-734C-B235-3E5DC5D519F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10710E4D-7165-DF46-A373-34A87777C43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,9 +240,6 @@
     <t>Whether the contributor explicitly references supporting evidence.</t>
   </si>
   <si>
-    <t>Only code if KS_present=1; otherwise null. Code 1 when the utterance explicitly invokes any supporting evidence: an external source (including reference to unlikced but findable sources); focal article content or feature; edit or page history; explicit Wikipedia policy/rule text; explicit proof of prior consensus; direct comparison against another article; evidence introduced earlier by another contributor. Explicit references to “the sources,” used in an article count when clearly used as support. The evidence may be weak, mistaken, or unavailable in the utterance. A premise or conclusion with no referenceable basis is 0. Do not treat the inferential connection itself as evidence; code that under KS_reasoning. Code appeals to common knolwedge, domain knowledge as KS_claim_present.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Whether the utterance coordinates an article edit by proposing one, announcing or reporting one, or refining one. </t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Code 1 when the utterance asserts, challenges, or qualifies knowledge relevant to the article or its evaluation. A question counts only when it asserts, presupposes, or challenges knowledge. Code 0 for headings, greetings, pure coordination, or a pure insult with no substantive position. KS and KI may both be 1.</t>
+  </si>
+  <si>
+    <t>Only code if KS_present=1; otherwise null. Code 1 when the utterance explicitly invokes any supporting evidence: an external source (including reference to unlikced but findable sources); focal article content or feature; edit or page history; explicit Wikipedia policy/rule text; explicit proof of prior consensus; direct comparison against another article; evidence introduced earlier by another contributor. Explicit references to “the sources,” used in an article count when clearly used as support. The evidence may be weak, mistaken, or unavailable in the utterance. A premise or conclusion with no referenceable basis is 0. Do not treat the inferential connection itself as evidence; code that under KS_reasoning. Code appeals to common knolwedge, domain knowledge, personal anecdotes as KS_claim_present.</t>
   </si>
 </sst>
 </file>
@@ -592,10 +592,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
@@ -641,7 +641,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>19</v>
@@ -703,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>27</v>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10710E4D-7165-DF46-A373-34A87777C43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A710A5-EF16-9644-98EB-8C94C02FA440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Core_Schema" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -243,9 +256,6 @@
     <t xml:space="preserve">Whether the utterance coordinates an article edit by proposing one, announcing or reporting one, or refining one. </t>
   </si>
   <si>
-    <t>Code 1 when the utterance proposes a future edit, announces or reports an enacted edit, or refines an edit to article content, wording, sourcing, scope, structure, placement, or media. The exact changed text or diff need not be visible when the utterance clearly refers to an article edit (for example, “I changed it”). Code 0 for a pure claim, objection, acceptance, rejection, or evaluation that does not also coordinate an edit; most such feedback is KS. Also code 0 for generic process or governance steps and for Talk-page/WikiProject assessment metadata such as article grade. Also code 0 for calls and offers to revert work. KS and KI may co-occur.</t>
-  </si>
-  <si>
     <t>Whether the utterance makes dispute-relevant knowledge public by asserting or challenging a claim, observation, interpretation, or constraint relevant to the article or dispute.</t>
   </si>
   <si>
@@ -253,6 +263,9 @@
   </si>
   <si>
     <t>Only code if KS_present=1; otherwise null. Code 1 when the utterance explicitly invokes any supporting evidence: an external source (including reference to unlikced but findable sources); focal article content or feature; edit or page history; explicit Wikipedia policy/rule text; explicit proof of prior consensus; direct comparison against another article; evidence introduced earlier by another contributor. Explicit references to “the sources,” used in an article count when clearly used as support. The evidence may be weak, mistaken, or unavailable in the utterance. A premise or conclusion with no referenceable basis is 0. Do not treat the inferential connection itself as evidence; code that under KS_reasoning. Code appeals to common knolwedge, domain knowledge, personal anecdotes as KS_claim_present.</t>
+  </si>
+  <si>
+    <t>Code 1 when the utterance discusses or proposes a future edit, announces or reports an enacted edit, or refines an edit to article content, wording, sourcing, scope, structure, placement, or media. The exact changed text or diff need not be visible when the utterance clearly refers to an article edit (for example, “I changed it”). Code 0 for a pure claim, objection, acceptance, rejection, or evaluation that does not also coordinate an edit; most such feedback is KS. Also code 0 for generic process or governance steps and for Talk-page/WikiProject assessment metadata such as article grade. Also code 0 for calls and offers to revert work. KS and KI may co-occur.</t>
   </si>
 </sst>
 </file>
@@ -592,10 +605,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
@@ -641,7 +654,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>19</v>
@@ -706,7 +719,7 @@
         <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>27</v>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B20BEF0-CA04-F547-B786-470D95FEEB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824EB44B-946C-3540-B6DA-79FFCFB76740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>binary {0,1}</t>
   </si>
   <si>
-    <t>Whether the utterance stakes dispute-relevant knowledge by asserting, challenging, qualifying, or limiting a position about the article or dispute.</t>
-  </si>
-  <si>
     <t>Code 1 when the utterance makes an article- or dispute-related knowledge claim, objection, interpretation, evaluation, or constraint public. A question counts when it asserts, presupposes, or challenges a proposition. Code 0 for headings, greetings, pure coordination, governance-only talk, claims unrelated to the article or dispute, and personal remarks with no substantive article-related position. If 0, all KS dimensions are null. If 1, code every KS dimension independently; dimensions may co-occur. KS and KI may also co-occur.</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance stake dispute-relevant knowledge by asserting, challenging, qualifying, or limiting an article- or dispute-related position?</t>
-  </si>
-  <si>
     <t>KS_explicit_reasoning</t>
   </si>
   <si>
@@ -100,13 +94,7 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance explicate an inferential link between a premise or evidence and a claim or conclusion?</t>
-  </si>
-  <si>
     <t>KS_grounding</t>
-  </si>
-  <si>
-    <t>Whether the utterance invokes identifiable evidence or a supporting basis for a stake.</t>
   </si>
   <si>
     <t>Only code if KS_present=1. Code 1 for a named, quoted, or linked source; article text or feature; edit or page history; Wikipedia policy or rule; documented consensus; or another article used as support. The evidence may be weak or contested. Code 0 for an unsupported assertion or general belief with no identifiable basis. Do not require an explanation of how the evidence supports the claim; that is KS_explicit_reasoning.</t>
@@ -124,9 +112,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance invoke/reference identifiable evidence or another basis of support?</t>
-  </si>
-  <si>
     <t>KS_new_evidence</t>
   </si>
   <si>
@@ -139,10 +124,13 @@
     <t>Only code if KS_grounding=1. Code 1 if at least one supporting basis appears for the first time in the dispute; otherwise code 0. Additional quotations, facts, or elaboration from already-shared evidence do not count as new.</t>
   </si>
   <si>
-    <t>Does the utterance introduce any evidence that has not previously appeared in the dispute?</t>
-  </si>
-  <si>
     <t>KS_restaking</t>
+  </si>
+  <si>
+    <t>Whether the utterance repeats a claim, objection, criterion, or position already made earlier in the dispute without adding new information.</t>
+  </si>
+  <si>
+    <t>Only code if KS_present=1. Code 1 when an earlier stake is repeated by the same or another contributor with no meaningful new information. Minor rewording counts as repetition. Code 0 if the utterance adds new evidence, reasoning, qualification, distinction, or other information, or if it is the first occurrence of the stake.</t>
   </si>
   <si>
     <t>Verbatim excerpt: “We have many different reliable sources each stating different dates. Do you see the issue?”
@@ -155,9 +143,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
 WikiDisputes archive; conv_id=253990014.204845.204845; utterance_index=21; repeats utterance_index=20
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
-  </si>
-  <si>
-    <t>Does the utterance restate a claim, objection, criterion, or position already made earlier in the dispute, without adding new information?</t>
   </si>
   <si>
     <t>KS_bounding</t>
@@ -189,12 +174,6 @@
   </si>
   <si>
     <t>KI_present</t>
-  </si>
-  <si>
-    <t>Whether the utterance translates dispute-relevant knowledge into an identifiable treatment of the shared article, by discussing, constructing, adapting, adopting, or enacting how contested material should be represented.</t>
-  </si>
-  <si>
-    <t>Code 1 only when BOTH conditions are met: (1) the utterance identifies an "article treatment" (i.e., what should be written, sourced, included, excluded, retained, relocated, structured, labeled, or displayed); AND (2) that treatment is shaped by a dispute-relevant claim, evidence item, distinction, objection, or constraint visible in the utterance or prior dialogue. The treatment may be implied, proposed, adapted, adopted, or enacted; it need not succeed or resolve the dispute. Code 0 for claims, evidence, reasoning, agreement, concession, or KS_bounding alone; requests for facts; generic process/governance steps; voting or reporting consensus alone; a vague 'this is wrong/does not belong'; or a bare revert/restoration of an already-contested version with no adaptation. A simple removal/addition counts only when it is an identifiable treatment flowing from the content problem under discussion. KS and KI may co-occur.</t>
   </si>
   <si>
     <t>Verbatim excerpt: “I've moved the element of critical evaluation into the Critical reaction section per your observation.”
@@ -221,9 +200,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance translate dispute-relevant knowledge into an identifiable treatment of the shared article?</t>
-  </si>
-  <si>
     <t>Controls</t>
   </si>
   <si>
@@ -244,9 +220,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance redirect discussion away from the current focal article problem to material with no plausible bearing on understanding or resolving it?</t>
-  </si>
-  <si>
     <t>C_interpersonal_attack_or_disrespect</t>
   </si>
   <si>
@@ -264,9 +237,6 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
-    <t>Does the utterance direct insult, ridicule, contempt, disrespect, bad-faith or motive attribution, or personal devaluation at a contributor or contributor group?</t>
-  </si>
-  <si>
     <t>C_formal_governance_action</t>
   </si>
   <si>
@@ -282,9 +252,6 @@
   <si>
     <t>WikiDisputes archive; conv_id=666161089.106.106; utterance_index=4
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
-  </si>
-  <si>
-    <t>Does the utterance propose, threaten, request, initiate, announce, or report moving the dispute into a recognized governance procedure or seeking authoritative intervention?</t>
   </si>
   <si>
     <t>Dispute Context</t>
@@ -309,9 +276,6 @@
 Do not infer the object from the resolution.</t>
   </si>
   <si>
-    <t>What is the main editorial question participants directly disagree about across the dispute?</t>
-  </si>
-  <si>
     <t>Dispute Outcome</t>
   </si>
   <si>
@@ -332,16 +296,52 @@
 5 = Clearly resolved: the focal disagreement is clearly treated as settled by the opposing sides and is not reopened.</t>
   </si>
   <si>
-    <t>By the end of the discussion, to what extent do the opposing sides treat the focal disagreement as settled?</t>
-  </si>
-  <si>
-    <t>Whether the utterance repeats a claim, objection, criterion, or position already made earlier in the dispute without adding new information.</t>
-  </si>
-  <si>
-    <t>Only code if KS_present=1. Code 1 when an earlier stake is repeated by the same or another contributor with no meaningful new information. Minor rewording counts as repetition. Code 0 if the utterance adds new evidence, reasoning, qualification, distinction, or other information, or if it is the first occurrence of the stake.</t>
-  </si>
-  <si>
-    <t>Does the utterance repeat a claim, objection, criterion, or position already made earlier in the dispute without adding new information?</t>
+    <t>Does it explain why a reason or evidence supports a claim?</t>
+  </si>
+  <si>
+    <t>Does it repeat an earlier position without new information?</t>
+  </si>
+  <si>
+    <t>Does it shift away from the focal article problem?</t>
+  </si>
+  <si>
+    <t>Does it attack or disrespect another contributor?</t>
+  </si>
+  <si>
+    <t>Does it invoke a formal dispute-resolution or enforcement process?</t>
+  </si>
+  <si>
+    <t>What is the dispute mainly about?</t>
+  </si>
+  <si>
+    <t>How settled is the focal disagreement by the end?</t>
+  </si>
+  <si>
+    <t>Is the evidence/support new to the dispute?</t>
+  </si>
+  <si>
+    <t>Code 1 only when BOTH conditions are met: (1) the utterance discusses an "article treatment" (i.e., what should/could be written, sourced, included, excluded, retained, relocated, structured, labeled, or displayed); AND (2) that treatment appears to be shaped by a dispute-relevant claim, evidence item, distinction, objection, or constraint visible in the utterance or prior dialogue. The treatment may be implied, proposed, adapted, adopted, or enacted; it need not succeed or resolve the dispute. Code 0 for claims, evidence, reasoning, agreement, concession, or KS_bounding alone; requests for facts; generic process/governance steps; voting or reporting consensus alone; a vague 'this is wrong/does not belong'; or a bare revert/restoration of an already-contested version with no adaptation. A simple removal/addition counts only when it is an identifiable treatment flowing from the content problem under discussion. KS and KI may co-occur.</t>
+  </si>
+  <si>
+    <t>Does it turn knowledge shared in the dispute into an article treatment?</t>
+  </si>
+  <si>
+    <t>Whether the utterance invokes identifiable evidence or a supporting basis for a staked claim</t>
+  </si>
+  <si>
+    <t>Whether the utterance stakes dispute-relevant knowledge by asserting, challenging, qualifying, or limiting a claim/position about the article or dispute.</t>
+  </si>
+  <si>
+    <t>Does the utterance assert, challenge, support, qualify, or limit a dispute-relevant knowledge claim?</t>
+  </si>
+  <si>
+    <t>Whether the utterance translates previosuly shared dispute-relevant knowledge into an identifiable treatment of the shared article, by suggesting, announcing (enactment of), coordianting, constructing, or accepting how contested material should be represented.</t>
+  </si>
+  <si>
+    <t>Does it signal conditions under which the speaker might accept a position, or revise their own?</t>
+  </si>
+  <si>
+    <t>Does it cite evidence for support?</t>
   </si>
 </sst>
 </file>
@@ -415,7 +415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -498,20 +498,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -530,31 +516,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -569,7 +540,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -584,7 +555,22 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,304 +823,304 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="115" customHeight="1">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:8" ht="165">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="210">
+      <c r="A3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="130" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="180">
+      <c r="A4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="135" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60">
+      <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="70" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="195">
+      <c r="A6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="342">
+      <c r="A7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="95" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="409.6">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="220" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="E8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H8" s="20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="105">
+      <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="165" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="B9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="75">
+      <c r="A10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="95" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="E10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="F10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="G10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="105">
+      <c r="A11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="F11" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="110" customHeight="1">
-      <c r="A10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="G11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="H11" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="210">
+      <c r="A12" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="B12" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="105" customHeight="1">
-      <c r="A11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="16" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="300">
+      <c r="A13" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="B13" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="120" customHeight="1">
-      <c r="A12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="23" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="175" customHeight="1">
-      <c r="A13" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824EB44B-946C-3540-B6DA-79FFCFB76740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4913BD69-B921-CA40-B04D-009B1EE7DBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
   <si>
     <t>Family</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>binary {0,1}</t>
+  </si>
+  <si>
+    <t>Whether the utterance stakes dispute-relevant knowledge by asserting, challenging, qualifying, or limiting a claim/position about the article or dispute.</t>
   </si>
   <si>
     <t>Code 1 when the utterance makes an article- or dispute-related knowledge claim, objection, interpretation, evaluation, or constraint public. A question counts when it asserts, presupposes, or challenges a proposition. Code 0 for headings, greetings, pure coordination, governance-only talk, claims unrelated to the article or dispute, and personal remarks with no substantive article-related position. If 0, all KS dimensions are null. If 1, code every KS dimension independently; dimensions may co-occur. KS and KI may also co-occur.</t>
@@ -70,6 +73,9 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
+    <t>Does the utterance assert, challenge, support, qualify, or limit a dispute-relevant knowledge claim?</t>
+  </si>
+  <si>
     <t>KS_explicit_reasoning</t>
   </si>
   <si>
@@ -94,7 +100,13 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
+    <t>Does it explain why a reason or evidence supports a claim?</t>
+  </si>
+  <si>
     <t>KS_grounding</t>
+  </si>
+  <si>
+    <t>Whether the utterance invokes identifiable evidence or a supporting basis for a staked claim</t>
   </si>
   <si>
     <t>Only code if KS_present=1. Code 1 for a named, quoted, or linked source; article text or feature; edit or page history; Wikipedia policy or rule; documented consensus; or another article used as support. The evidence may be weak or contested. Code 0 for an unsupported assertion or general belief with no identifiable basis. Do not require an explanation of how the evidence supports the claim; that is KS_explicit_reasoning.</t>
@@ -112,6 +124,9 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
+    <t>Does it cite evidence for support?</t>
+  </si>
+  <si>
     <t>KS_new_evidence</t>
   </si>
   <si>
@@ -122,6 +137,9 @@
   </si>
   <si>
     <t>Only code if KS_grounding=1. Code 1 if at least one supporting basis appears for the first time in the dispute; otherwise code 0. Additional quotations, facts, or elaboration from already-shared evidence do not count as new.</t>
+  </si>
+  <si>
+    <t>Is the evidence/support new to the dispute?</t>
   </si>
   <si>
     <t>KS_restaking</t>
@@ -143,6 +161,9 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
 WikiDisputes archive; conv_id=253990014.204845.204845; utterance_index=21; repeats utterance_index=20
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
+  </si>
+  <si>
+    <t>Does it repeat an earlier position without new information?</t>
   </si>
   <si>
     <t>KS_bounding</t>
@@ -170,34 +191,7 @@
 WikiDisputes; source_row_uid=wdrow:v1:eeef3f25985585f8141b22505c01ca448251865d26fe339ca42ea806e4be125f; speaker=DigitalC; 2008.</t>
   </si>
   <si>
-    <t>Knowledge Integration</t>
-  </si>
-  <si>
-    <t>KI_present</t>
-  </si>
-  <si>
-    <t>Verbatim excerpt: “I've moved the element of critical evaluation into the Critical reaction section per your observation.”
-Explanation: Code 1. A prior observation becomes consequential for article placement; the speaker enacts a treatment shaped by dispute knowledge.
-Verbatim excerpt: “Okay, well how about we call it "Civilians" or "Civilians and non-combatants" instead?”
-Explanation: Code 1. The candidate wording turns the disputed category/label issue into an identifiable article treatment.
-Verbatim excerpt: “OK, I cut the text down from one of the pictures, and "hid" some of the text for another. Is this any better?”
-Explanation: Code 1. The speaker adapts an article treatment in response to prior concerns and puts the revised treatment back into the dialogue for assessment.
-Verbatim excerpt: “I have been bold and and added examples of white people who are undisputably white in an attempt to resolve the dispute of which examples should be shown due to dispute over who is considered white.”
-Explanation: Code 1. The speaker enacts a representational change intended to address the disputed classification problem.
-Verbatim excerpt: “NASA claims no such thing happened, you can check the data. According to data the solar eclipse occurred on the 28th day of Ramadan, not the 15th…”
-Explanation: Code 0. This stakes a factual claim, but does not itself specify or enact an article treatment.</t>
-  </si>
-  <si>
-    <t>WikiDisputes archive; conv_id=250753818.16809.16809; utterance_index=6
-https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
-WikiDisputes archive; conv_id=253990014.204845.204845; utterance_index=7
-https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
-WikiDisputes archive; conv_id=241542926.24311.24311; utterance_index=23
-https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
-WikiDisputes archive; conv_id=241542926.24311.24311; utterance_index=15
-https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz
-WikiDisputes archive; conv_id=651773317.68513.68513; utterance_index=6
-https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
+    <t>Does it signal conditions under which the speaker might accept a position, or revise their own?</t>
   </si>
   <si>
     <t>Controls</t>
@@ -220,6 +214,9 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
+    <t>Does it shift away from the focal article problem?</t>
+  </si>
+  <si>
     <t>C_interpersonal_attack_or_disrespect</t>
   </si>
   <si>
@@ -237,6 +234,9 @@
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
   </si>
   <si>
+    <t>Does it attack or disrespect another contributor?</t>
+  </si>
+  <si>
     <t>C_formal_governance_action</t>
   </si>
   <si>
@@ -252,6 +252,9 @@
   <si>
     <t>WikiDisputes archive; conv_id=666161089.106.106; utterance_index=4
 https://github.com/christinedekock11/wikidisputes/blob/b6f5906179724969a883ebf3012064765edf133e/data.tar.gz</t>
+  </si>
+  <si>
+    <t>Does it invoke a formal dispute-resolution or enforcement process?</t>
   </si>
   <si>
     <t>Dispute Context</t>
@@ -276,6 +279,9 @@
 Do not infer the object from the resolution.</t>
   </si>
   <si>
+    <t>What is the dispute mainly about?</t>
+  </si>
+  <si>
     <t>Dispute Outcome</t>
   </si>
   <si>
@@ -296,52 +302,56 @@
 5 = Clearly resolved: the focal disagreement is clearly treated as settled by the opposing sides and is not reopened.</t>
   </si>
   <si>
-    <t>Does it explain why a reason or evidence supports a claim?</t>
-  </si>
-  <si>
-    <t>Does it repeat an earlier position without new information?</t>
-  </si>
-  <si>
-    <t>Does it shift away from the focal article problem?</t>
-  </si>
-  <si>
-    <t>Does it attack or disrespect another contributor?</t>
-  </si>
-  <si>
-    <t>Does it invoke a formal dispute-resolution or enforcement process?</t>
-  </si>
-  <si>
-    <t>What is the dispute mainly about?</t>
-  </si>
-  <si>
     <t>How settled is the focal disagreement by the end?</t>
   </si>
   <si>
-    <t>Is the evidence/support new to the dispute?</t>
-  </si>
-  <si>
-    <t>Code 1 only when BOTH conditions are met: (1) the utterance discusses an "article treatment" (i.e., what should/could be written, sourced, included, excluded, retained, relocated, structured, labeled, or displayed); AND (2) that treatment appears to be shaped by a dispute-relevant claim, evidence item, distinction, objection, or constraint visible in the utterance or prior dialogue. The treatment may be implied, proposed, adapted, adopted, or enacted; it need not succeed or resolve the dispute. Code 0 for claims, evidence, reasoning, agreement, concession, or KS_bounding alone; requests for facts; generic process/governance steps; voting or reporting consensus alone; a vague 'this is wrong/does not belong'; or a bare revert/restoration of an already-contested version with no adaptation. A simple removal/addition counts only when it is an identifiable treatment flowing from the content problem under discussion. KS and KI may co-occur.</t>
-  </si>
-  <si>
-    <t>Does it turn knowledge shared in the dispute into an article treatment?</t>
-  </si>
-  <si>
-    <t>Whether the utterance invokes identifiable evidence or a supporting basis for a staked claim</t>
-  </si>
-  <si>
-    <t>Whether the utterance stakes dispute-relevant knowledge by asserting, challenging, qualifying, or limiting a claim/position about the article or dispute.</t>
-  </si>
-  <si>
-    <t>Does the utterance assert, challenge, support, qualify, or limit a dispute-relevant knowledge claim?</t>
-  </si>
-  <si>
-    <t>Whether the utterance translates previosuly shared dispute-relevant knowledge into an identifiable treatment of the shared article, by suggesting, announcing (enactment of), coordianting, constructing, or accepting how contested material should be represented.</t>
-  </si>
-  <si>
-    <t>Does it signal conditions under which the speaker might accept a position, or revise their own?</t>
-  </si>
-  <si>
-    <t>Does it cite evidence for support?</t>
+    <t>Knowledge Integration</t>
+  </si>
+  <si>
+    <t>KI_coordinating_edits</t>
+  </si>
+  <si>
+    <t>Whether the utterance helps coordinate changes to the Wikipedia page by proposing, planning, requesting, discussing, carrying out, reporting, or refining an edit or the concrete article treatment needed for one.</t>
+  </si>
+  <si>
+    <t>Code 1 when the utterance advances a concrete page-edit decision or implementation: for example, adding/removing/replacing/rephrasing/moving/renaming/restructuring/tagging/sourcing material; asking or answering an edit-specific question; reporting an edit or fix; or supplying material explicitly for an edit. The edit need not be agreed, successful, or already enacted, and the utterance may also contain Knowledge Staking. Code 0 for a claim, objection, evidence discussion, or evaluation with no identifiable edit coordination; a generic call for consensus/cooperation; or formal governance/escalation alone. Do NOT require compromise. Code independently of KI_compromise. Overall Knowledge Integration = 1 when KI_coordinating_edits=1 OR KI_compromise=1.</t>
+  </si>
+  <si>
+    <t>Verbatim excerpt: “I've changed the article to meet the accessibility guidelines for best practices located at MOS:LISTGAP.”
+Explanation: The contributor reports a concrete enacted change to the article. This is edit coordination even though no compromise is offered.</t>
+  </si>
+  <si>
+    <t>WikiDisputes escalated.json; conv_id=745334414.6152.6152; utterance_id=745411397.6830.6830; page=List of state leaders in the 10th century
+https://github.com/christinedekock11/wikidisputes/blob/main/data.tar.gz
+Definition basis: De Kock et al. (2022), Table 4: https://aclanthology.org/2022.emnlp-main.252.pdf
+Annotation behavior checked against final WikiTactics: https://github.com/christinedekock11/wikitactics/blob/master/wikitactics.json
+Exclusion check: this conv_id is absent from the final WikiTactics dataset and the current gold files.</t>
+  </si>
+  <si>
+    <t>Does the utterance coordinate a concrete change to the Wikipedia page?</t>
+  </si>
+  <si>
+    <t>KI_compromise</t>
+  </si>
+  <si>
+    <t>Code 1 when the speaker makes a conciliatory offer or proposal aimed at bridging the disagreement: for example, explicitly proposes a compromise; preserves or combines meaningful elements of opposed positions; offers a partial concession or alternative arrangement to make agreement possible; or offers to repair cooperation. The compromise need not be accepted or succeed, and it need not itself specify a page edit. Code 0 for merely restating one's preferred position, proposing a different edit with no visible accommodation, accepting/conceding outright without a bridging offer, a generic request for consensus, or saying an option would settle the issue without offering accommodation. Code independently of KI_coordinating_edits; both may be 1. Overall Knowledge Integration = 1 when KI_coordinating_edits=1 OR KI_compromise=1.</t>
+  </si>
+  <si>
+    <t>Verbatim excerpt: “But how about a compromise, we'll keep the section the way it is now, but get rid of the line ‘But Interstate Football was still hugely popular in Victoria’, and add ‘Interstate Football was still very popular in Victoria’.”
+Explanation: The contributor explicitly offers a middle-ground treatment that preserves the section while softening the disputed wording. This is KI_compromise=1 and also coordinates an edit.</t>
+  </si>
+  <si>
+    <t>WikiDisputes escalated.json; conv_id=666593496.5192.5192; utterance_id=667023397.11214.11214; page=SportsEditor518
+https://github.com/christinedekock11/wikidisputes/blob/main/data.tar.gz
+Definition basis: De Kock et al. (2022), Table 4: https://aclanthology.org/2022.emnlp-main.252.pdf
+Annotation behavior checked against final WikiTactics: https://github.com/christinedekock11/wikitactics/blob/master/wikitactics.json
+Exclusion check: this conv_id is absent from the final WikiTactics dataset and the current gold files.</t>
+  </si>
+  <si>
+    <t>Does the utterance offer a middle ground or accommodation intended to bridge the disagreement?</t>
+  </si>
+  <si>
+    <t>Whether the utterance offers a compromise or accommodation intended to bridge opposed positions or restore workable cooperation. An clear attempt to find a midway between the speaker's point and the opposer's.</t>
   </si>
 </sst>
 </file>
@@ -785,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -834,19 +844,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="210">
@@ -854,25 +864,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="180">
@@ -880,25 +890,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60">
@@ -906,21 +916,21 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="19" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="195">
@@ -928,25 +938,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="342">
@@ -954,108 +964,108 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="409.6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="150" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" s="5" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="H8" s="20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="150" customHeight="1">
+      <c r="A9" s="16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="105">
-      <c r="A9" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="B9" s="11" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="105">
+      <c r="A10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="B10" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="75">
-      <c r="A10" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="105">
+    </row>
+    <row r="11" spans="1:8" ht="75">
       <c r="A11" s="16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>53</v>
@@ -1076,51 +1086,75 @@
         <v>57</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="210">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="105">
       <c r="A12" s="17" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="H12" s="22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="300">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="210">
       <c r="A13" s="18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
         <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/codebook.xlsx
+++ b/data/source/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leopallen/Documents/research/wikipedia_discourse/human_annotation_tool/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4913BD69-B921-CA40-B04D-009B1EE7DBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81891F7F-001A-2E4A-A035-DCB784500088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,9 +328,6 @@
 Exclusion check: this conv_id is absent from the final WikiTactics dataset and the current gold files.</t>
   </si>
   <si>
-    <t>Does the utterance coordinate a concrete change to the Wikipedia page?</t>
-  </si>
-  <si>
     <t>KI_compromise</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>Whether the utterance offers a compromise or accommodation intended to bridge opposed positions or restore workable cooperation. An clear attempt to find a midway between the speaker's point and the opposer's.</t>
+  </si>
+  <si>
+    <t>Does the utterance attempt to coordinate an update to the Wikipedia page?</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1008,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="150" customHeight="1">
@@ -1016,25 +1016,25 @@
         <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="21" t="s">
         <v>87</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="105">
